--- a/01_data/raw_data/Burraco_et_al_hibernation_hibernation.xlsx
+++ b/01_data/raw_data/Burraco_et_al_hibernation_hibernation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pablocapillalasheras/Library/CloudStorage/Dropbox/PabloCL/2-Work drive/3-Active_projects/8 - Collaborations/01_Meta-analysis_hibernation/meta_analysis_hibernation/01_data/raw_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF16E23A-1557-614D-B6C4-8EBE80563BDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B7DA4F5-3959-0543-90EC-2CEF029360CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19520" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4680" yWindow="22260" windowWidth="30240" windowHeight="17500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="All_OS" sheetId="2" r:id="rId1"/>
@@ -54484,8 +54484,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:U239"/>
+  <dimension ref="A1:U238"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="29.83203125" style="15" customWidth="1"/>
@@ -54577,7 +54576,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="2" spans="1:21" hidden="1">
+    <row r="2" spans="1:21">
       <c r="A2" s="15" t="s">
         <v>719</v>
       </c>
@@ -54627,7 +54626,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="3" spans="1:21" hidden="1">
+    <row r="3" spans="1:21">
       <c r="A3" s="15" t="s">
         <v>719</v>
       </c>
@@ -54677,7 +54676,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="4" spans="1:21" hidden="1">
+    <row r="4" spans="1:21">
       <c r="A4" s="15" t="s">
         <v>719</v>
       </c>
@@ -55388,7 +55387,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="16" spans="1:21" hidden="1">
+    <row r="16" spans="1:21">
       <c r="A16" s="15" t="s">
         <v>721</v>
       </c>
@@ -55438,7 +55437,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="17" spans="1:21" hidden="1">
+    <row r="17" spans="1:21">
       <c r="A17" s="15" t="s">
         <v>721</v>
       </c>
@@ -55488,7 +55487,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="1:21" hidden="1">
+    <row r="18" spans="1:21">
       <c r="A18" s="15" t="s">
         <v>721</v>
       </c>
@@ -55538,7 +55537,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="1:21" hidden="1">
+    <row r="19" spans="1:21">
       <c r="A19" s="15" t="s">
         <v>722</v>
       </c>
@@ -55599,7 +55598,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="20" spans="1:21" hidden="1">
+    <row r="20" spans="1:21">
       <c r="A20" s="15" t="s">
         <v>722</v>
       </c>
@@ -55660,7 +55659,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="21" spans="1:21" hidden="1">
+    <row r="21" spans="1:21">
       <c r="A21" s="15" t="s">
         <v>722</v>
       </c>
@@ -55721,7 +55720,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="22" spans="1:21" hidden="1">
+    <row r="22" spans="1:21">
       <c r="A22" s="15" t="s">
         <v>722</v>
       </c>
@@ -55782,7 +55781,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:21" hidden="1">
+    <row r="23" spans="1:21">
       <c r="A23" s="15" t="s">
         <v>722</v>
       </c>
@@ -55843,7 +55842,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="24" spans="1:21" hidden="1">
+    <row r="24" spans="1:21">
       <c r="A24" s="15" t="s">
         <v>722</v>
       </c>
@@ -55904,7 +55903,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="25" spans="1:21" hidden="1">
+    <row r="25" spans="1:21">
       <c r="A25" s="15" t="s">
         <v>722</v>
       </c>
@@ -55965,7 +55964,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="26" spans="1:21" hidden="1">
+    <row r="26" spans="1:21">
       <c r="A26" s="15" t="s">
         <v>722</v>
       </c>
@@ -56026,7 +56025,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="27" spans="1:21" hidden="1">
+    <row r="27" spans="1:21">
       <c r="A27" s="15" t="s">
         <v>722</v>
       </c>
@@ -56087,7 +56086,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="28" spans="1:21" hidden="1">
+    <row r="28" spans="1:21">
       <c r="A28" s="15" t="s">
         <v>722</v>
       </c>
@@ -56148,7 +56147,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="29" spans="1:21" hidden="1">
+    <row r="29" spans="1:21">
       <c r="A29" s="15" t="s">
         <v>722</v>
       </c>
@@ -56209,7 +56208,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="30" spans="1:21" hidden="1">
+    <row r="30" spans="1:21">
       <c r="A30" s="15" t="s">
         <v>722</v>
       </c>
@@ -56270,7 +56269,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="31" spans="1:21" hidden="1">
+    <row r="31" spans="1:21">
       <c r="A31" s="15" t="s">
         <v>722</v>
       </c>
@@ -56331,7 +56330,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="32" spans="1:21" hidden="1">
+    <row r="32" spans="1:21">
       <c r="A32" s="15" t="s">
         <v>722</v>
       </c>
@@ -56392,7 +56391,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="33" spans="1:21" hidden="1">
+    <row r="33" spans="1:21">
       <c r="A33" s="15" t="s">
         <v>722</v>
       </c>
@@ -56453,7 +56452,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="34" spans="1:21" hidden="1">
+    <row r="34" spans="1:21">
       <c r="A34" s="15" t="s">
         <v>723</v>
       </c>
@@ -56512,7 +56511,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="35" spans="1:21" hidden="1">
+    <row r="35" spans="1:21">
       <c r="A35" s="15" t="s">
         <v>723</v>
       </c>
@@ -56571,7 +56570,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="36" spans="1:21" hidden="1">
+    <row r="36" spans="1:21">
       <c r="A36" s="15" t="s">
         <v>723</v>
       </c>
@@ -56630,7 +56629,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="37" spans="1:21" hidden="1">
+    <row r="37" spans="1:21">
       <c r="A37" s="15" t="s">
         <v>723</v>
       </c>
@@ -56689,7 +56688,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="38" spans="1:21" hidden="1">
+    <row r="38" spans="1:21">
       <c r="A38" s="15" t="s">
         <v>723</v>
       </c>
@@ -56748,7 +56747,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="39" spans="1:21" hidden="1">
+    <row r="39" spans="1:21">
       <c r="A39" s="15" t="s">
         <v>723</v>
       </c>
@@ -56807,7 +56806,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="40" spans="1:21" hidden="1">
+    <row r="40" spans="1:21">
       <c r="A40" s="15" t="s">
         <v>723</v>
       </c>
@@ -56866,7 +56865,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="41" spans="1:21" hidden="1">
+    <row r="41" spans="1:21">
       <c r="A41" s="15" t="s">
         <v>723</v>
       </c>
@@ -56925,7 +56924,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="42" spans="1:21" hidden="1">
+    <row r="42" spans="1:21">
       <c r="A42" s="15" t="s">
         <v>724</v>
       </c>
@@ -56984,7 +56983,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="43" spans="1:21" hidden="1">
+    <row r="43" spans="1:21">
       <c r="A43" s="15" t="s">
         <v>724</v>
       </c>
@@ -57043,7 +57042,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="44" spans="1:21" hidden="1">
+    <row r="44" spans="1:21">
       <c r="A44" s="15" t="s">
         <v>724</v>
       </c>
@@ -57102,7 +57101,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="45" spans="1:21" hidden="1">
+    <row r="45" spans="1:21">
       <c r="A45" s="15" t="s">
         <v>724</v>
       </c>
@@ -57158,7 +57157,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="46" spans="1:21" hidden="1">
+    <row r="46" spans="1:21">
       <c r="A46" s="15" t="s">
         <v>724</v>
       </c>
@@ -57217,7 +57216,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="47" spans="1:21" hidden="1">
+    <row r="47" spans="1:21">
       <c r="A47" s="15" t="s">
         <v>724</v>
       </c>
@@ -57276,7 +57275,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="48" spans="1:21" hidden="1">
+    <row r="48" spans="1:21">
       <c r="A48" s="15" t="s">
         <v>725</v>
       </c>
@@ -57326,7 +57325,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="49" spans="1:21" hidden="1">
+    <row r="49" spans="1:21">
       <c r="A49" s="15" t="s">
         <v>725</v>
       </c>
@@ -57376,7 +57375,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="50" spans="1:21" hidden="1">
+    <row r="50" spans="1:21">
       <c r="A50" s="15" t="s">
         <v>725</v>
       </c>
@@ -57426,7 +57425,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="51" spans="1:21" hidden="1">
+    <row r="51" spans="1:21">
       <c r="A51" s="15" t="s">
         <v>725</v>
       </c>
@@ -57476,7 +57475,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="52" spans="1:21" hidden="1">
+    <row r="52" spans="1:21">
       <c r="A52" s="15" t="s">
         <v>725</v>
       </c>
@@ -57526,7 +57525,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="53" spans="1:21" hidden="1">
+    <row r="53" spans="1:21">
       <c r="A53" s="15" t="s">
         <v>725</v>
       </c>
@@ -57576,7 +57575,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="54" spans="1:21" hidden="1">
+    <row r="54" spans="1:21">
       <c r="A54" s="15" t="s">
         <v>725</v>
       </c>
@@ -57626,7 +57625,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="55" spans="1:21" hidden="1">
+    <row r="55" spans="1:21">
       <c r="A55" s="15" t="s">
         <v>725</v>
       </c>
@@ -57676,7 +57675,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="56" spans="1:21" hidden="1">
+    <row r="56" spans="1:21">
       <c r="A56" s="15" t="s">
         <v>725</v>
       </c>
@@ -57726,7 +57725,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="57" spans="1:21" hidden="1">
+    <row r="57" spans="1:21">
       <c r="A57" s="15" t="s">
         <v>725</v>
       </c>
@@ -57776,7 +57775,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="58" spans="1:21" hidden="1">
+    <row r="58" spans="1:21">
       <c r="A58" s="15" t="s">
         <v>285</v>
       </c>
@@ -57835,7 +57834,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="59" spans="1:21" hidden="1">
+    <row r="59" spans="1:21">
       <c r="A59" s="15" t="s">
         <v>285</v>
       </c>
@@ -57894,7 +57893,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="60" spans="1:21" hidden="1">
+    <row r="60" spans="1:21">
       <c r="A60" s="15" t="s">
         <v>285</v>
       </c>
@@ -57953,7 +57952,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="61" spans="1:21" hidden="1">
+    <row r="61" spans="1:21">
       <c r="A61" s="15" t="s">
         <v>285</v>
       </c>
@@ -58012,7 +58011,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="62" spans="1:21" hidden="1">
+    <row r="62" spans="1:21">
       <c r="A62" s="15" t="s">
         <v>285</v>
       </c>
@@ -58071,7 +58070,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="63" spans="1:21" hidden="1">
+    <row r="63" spans="1:21">
       <c r="A63" s="15" t="s">
         <v>285</v>
       </c>
@@ -58130,7 +58129,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="64" spans="1:21" hidden="1">
+    <row r="64" spans="1:21">
       <c r="A64" s="15" t="s">
         <v>285</v>
       </c>
@@ -58189,7 +58188,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="65" spans="1:21" hidden="1">
+    <row r="65" spans="1:21">
       <c r="A65" s="15" t="s">
         <v>285</v>
       </c>
@@ -58248,7 +58247,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="66" spans="1:21" hidden="1">
+    <row r="66" spans="1:21">
       <c r="A66" s="15" t="s">
         <v>285</v>
       </c>
@@ -58307,7 +58306,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="67" spans="1:21" hidden="1">
+    <row r="67" spans="1:21">
       <c r="A67" s="15" t="s">
         <v>285</v>
       </c>
@@ -58366,7 +58365,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="68" spans="1:21" hidden="1">
+    <row r="68" spans="1:21">
       <c r="A68" s="15" t="s">
         <v>285</v>
       </c>
@@ -58425,7 +58424,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="69" spans="1:21" hidden="1">
+    <row r="69" spans="1:21">
       <c r="A69" s="15" t="s">
         <v>285</v>
       </c>
@@ -58484,7 +58483,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="70" spans="1:21" hidden="1">
+    <row r="70" spans="1:21">
       <c r="A70" s="15" t="s">
         <v>285</v>
       </c>
@@ -58543,7 +58542,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="71" spans="1:21" hidden="1">
+    <row r="71" spans="1:21">
       <c r="A71" s="15" t="s">
         <v>285</v>
       </c>
@@ -58602,7 +58601,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="72" spans="1:21" hidden="1">
+    <row r="72" spans="1:21">
       <c r="A72" s="15" t="s">
         <v>285</v>
       </c>
@@ -58661,7 +58660,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="73" spans="1:21" hidden="1">
+    <row r="73" spans="1:21">
       <c r="A73" s="15" t="s">
         <v>285</v>
       </c>
@@ -58720,7 +58719,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="74" spans="1:21" hidden="1">
+    <row r="74" spans="1:21">
       <c r="A74" s="15" t="s">
         <v>285</v>
       </c>
@@ -58773,7 +58772,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="75" spans="1:21" hidden="1">
+    <row r="75" spans="1:21">
       <c r="A75" s="15" t="s">
         <v>285</v>
       </c>
@@ -58832,7 +58831,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="76" spans="1:21" hidden="1">
+    <row r="76" spans="1:21">
       <c r="A76" s="15" t="s">
         <v>285</v>
       </c>
@@ -58891,7 +58890,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="77" spans="1:21" hidden="1">
+    <row r="77" spans="1:21">
       <c r="A77" s="15" t="s">
         <v>285</v>
       </c>
@@ -58950,7 +58949,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="78" spans="1:21" hidden="1">
+    <row r="78" spans="1:21">
       <c r="A78" s="15" t="s">
         <v>285</v>
       </c>
@@ -59009,7 +59008,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="79" spans="1:21" hidden="1">
+    <row r="79" spans="1:21">
       <c r="A79" s="15" t="s">
         <v>285</v>
       </c>
@@ -59068,7 +59067,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="80" spans="1:21" hidden="1">
+    <row r="80" spans="1:21">
       <c r="A80" s="15" t="s">
         <v>285</v>
       </c>
@@ -59127,7 +59126,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="81" spans="1:21" hidden="1">
+    <row r="81" spans="1:21">
       <c r="A81" s="15" t="s">
         <v>285</v>
       </c>
@@ -59186,7 +59185,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="82" spans="1:21" hidden="1">
+    <row r="82" spans="1:21">
       <c r="A82" s="15" t="s">
         <v>285</v>
       </c>
@@ -59245,7 +59244,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="83" spans="1:21" hidden="1">
+    <row r="83" spans="1:21">
       <c r="A83" s="15" t="s">
         <v>285</v>
       </c>
@@ -59304,7 +59303,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="84" spans="1:21" hidden="1">
+    <row r="84" spans="1:21">
       <c r="A84" s="15" t="s">
         <v>285</v>
       </c>
@@ -59363,7 +59362,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="85" spans="1:21" hidden="1">
+    <row r="85" spans="1:21">
       <c r="A85" s="15" t="s">
         <v>285</v>
       </c>
@@ -59422,7 +59421,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="86" spans="1:21" hidden="1">
+    <row r="86" spans="1:21">
       <c r="A86" s="15" t="s">
         <v>285</v>
       </c>
@@ -59481,7 +59480,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="87" spans="1:21" hidden="1">
+    <row r="87" spans="1:21">
       <c r="A87" s="15" t="s">
         <v>285</v>
       </c>
@@ -59540,7 +59539,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="88" spans="1:21" hidden="1">
+    <row r="88" spans="1:21">
       <c r="A88" s="15" t="s">
         <v>285</v>
       </c>
@@ -59599,7 +59598,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="89" spans="1:21" hidden="1">
+    <row r="89" spans="1:21">
       <c r="A89" s="15" t="s">
         <v>285</v>
       </c>
@@ -59658,7 +59657,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="90" spans="1:21" hidden="1">
+    <row r="90" spans="1:21">
       <c r="A90" s="15" t="s">
         <v>285</v>
       </c>
@@ -59717,7 +59716,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="91" spans="1:21" hidden="1">
+    <row r="91" spans="1:21">
       <c r="A91" s="15" t="s">
         <v>285</v>
       </c>
@@ -59776,7 +59775,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="92" spans="1:21" hidden="1">
+    <row r="92" spans="1:21">
       <c r="A92" s="15" t="s">
         <v>285</v>
       </c>
@@ -59835,7 +59834,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="93" spans="1:21" hidden="1">
+    <row r="93" spans="1:21">
       <c r="A93" s="15" t="s">
         <v>285</v>
       </c>
@@ -59894,7 +59893,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="94" spans="1:21" hidden="1">
+    <row r="94" spans="1:21">
       <c r="A94" s="15" t="s">
         <v>285</v>
       </c>
@@ -59953,7 +59952,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="95" spans="1:21" hidden="1">
+    <row r="95" spans="1:21">
       <c r="A95" s="15" t="s">
         <v>285</v>
       </c>
@@ -60012,7 +60011,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="96" spans="1:21" hidden="1">
+    <row r="96" spans="1:21">
       <c r="A96" s="15" t="s">
         <v>285</v>
       </c>
@@ -60071,7 +60070,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="97" spans="1:21" hidden="1">
+    <row r="97" spans="1:21">
       <c r="A97" s="15" t="s">
         <v>285</v>
       </c>
@@ -60130,7 +60129,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="98" spans="1:21" hidden="1">
+    <row r="98" spans="1:21">
       <c r="A98" s="15" t="s">
         <v>285</v>
       </c>
@@ -60189,7 +60188,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="99" spans="1:21" hidden="1">
+    <row r="99" spans="1:21">
       <c r="A99" s="15" t="s">
         <v>285</v>
       </c>
@@ -60248,7 +60247,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="100" spans="1:21" hidden="1">
+    <row r="100" spans="1:21">
       <c r="A100" s="15" t="s">
         <v>726</v>
       </c>
@@ -60307,7 +60306,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="101" spans="1:21" hidden="1">
+    <row r="101" spans="1:21">
       <c r="A101" s="15" t="s">
         <v>726</v>
       </c>
@@ -60366,7 +60365,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="102" spans="1:21" hidden="1">
+    <row r="102" spans="1:21">
       <c r="A102" s="15" t="s">
         <v>726</v>
       </c>
@@ -60425,7 +60424,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="103" spans="1:21" hidden="1">
+    <row r="103" spans="1:21">
       <c r="A103" s="15" t="s">
         <v>726</v>
       </c>
@@ -60484,7 +60483,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="104" spans="1:21" hidden="1">
+    <row r="104" spans="1:21">
       <c r="A104" s="15" t="s">
         <v>726</v>
       </c>
@@ -60543,7 +60542,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="105" spans="1:21" hidden="1">
+    <row r="105" spans="1:21">
       <c r="A105" s="15" t="s">
         <v>264</v>
       </c>
@@ -60602,7 +60601,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="106" spans="1:21" hidden="1">
+    <row r="106" spans="1:21">
       <c r="A106" s="15" t="s">
         <v>264</v>
       </c>
@@ -60661,7 +60660,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="107" spans="1:21" hidden="1">
+    <row r="107" spans="1:21">
       <c r="A107" s="15" t="s">
         <v>264</v>
       </c>
@@ -60720,7 +60719,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="108" spans="1:21" hidden="1">
+    <row r="108" spans="1:21">
       <c r="A108" s="15" t="s">
         <v>264</v>
       </c>
@@ -60779,7 +60778,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="109" spans="1:21" hidden="1">
+    <row r="109" spans="1:21">
       <c r="A109" s="15" t="s">
         <v>264</v>
       </c>
@@ -60838,7 +60837,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="110" spans="1:21" hidden="1">
+    <row r="110" spans="1:21">
       <c r="A110" s="15" t="s">
         <v>264</v>
       </c>
@@ -60897,7 +60896,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="111" spans="1:21" hidden="1">
+    <row r="111" spans="1:21">
       <c r="A111" s="15" t="s">
         <v>264</v>
       </c>
@@ -60956,7 +60955,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="112" spans="1:21" hidden="1">
+    <row r="112" spans="1:21">
       <c r="A112" s="15" t="s">
         <v>264</v>
       </c>
@@ -61015,7 +61014,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="113" spans="1:21" hidden="1">
+    <row r="113" spans="1:21">
       <c r="A113" s="15" t="s">
         <v>264</v>
       </c>
@@ -61074,7 +61073,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="114" spans="1:21" hidden="1">
+    <row r="114" spans="1:21">
       <c r="A114" s="15" t="s">
         <v>264</v>
       </c>
@@ -61133,7 +61132,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="115" spans="1:21" hidden="1">
+    <row r="115" spans="1:21">
       <c r="A115" s="15" t="s">
         <v>264</v>
       </c>
@@ -61192,7 +61191,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="116" spans="1:21" hidden="1">
+    <row r="116" spans="1:21">
       <c r="A116" s="15" t="s">
         <v>264</v>
       </c>
@@ -61251,7 +61250,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="117" spans="1:21" hidden="1">
+    <row r="117" spans="1:21">
       <c r="A117" s="15" t="s">
         <v>264</v>
       </c>
@@ -61310,7 +61309,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="118" spans="1:21" hidden="1">
+    <row r="118" spans="1:21">
       <c r="A118" s="15" t="s">
         <v>264</v>
       </c>
@@ -61369,7 +61368,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="119" spans="1:21" hidden="1">
+    <row r="119" spans="1:21">
       <c r="A119" s="15" t="s">
         <v>264</v>
       </c>
@@ -61428,7 +61427,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="120" spans="1:21" hidden="1">
+    <row r="120" spans="1:21">
       <c r="A120" s="15" t="s">
         <v>264</v>
       </c>
@@ -61487,7 +61486,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="121" spans="1:21" hidden="1">
+    <row r="121" spans="1:21">
       <c r="A121" s="15" t="s">
         <v>264</v>
       </c>
@@ -61546,7 +61545,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="122" spans="1:21" hidden="1">
+    <row r="122" spans="1:21">
       <c r="A122" s="15" t="s">
         <v>264</v>
       </c>
@@ -61605,7 +61604,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="123" spans="1:21" hidden="1">
+    <row r="123" spans="1:21">
       <c r="A123" s="15" t="s">
         <v>264</v>
       </c>
@@ -61664,7 +61663,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="124" spans="1:21" hidden="1">
+    <row r="124" spans="1:21">
       <c r="A124" s="15" t="s">
         <v>264</v>
       </c>
@@ -61723,7 +61722,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="125" spans="1:21" hidden="1">
+    <row r="125" spans="1:21">
       <c r="A125" s="15" t="s">
         <v>264</v>
       </c>
@@ -61782,7 +61781,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="126" spans="1:21" hidden="1">
+    <row r="126" spans="1:21">
       <c r="A126" s="15" t="s">
         <v>264</v>
       </c>
@@ -61841,7 +61840,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="127" spans="1:21" hidden="1">
+    <row r="127" spans="1:21">
       <c r="A127" s="15" t="s">
         <v>264</v>
       </c>
@@ -61900,7 +61899,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="128" spans="1:21" hidden="1">
+    <row r="128" spans="1:21">
       <c r="A128" s="15" t="s">
         <v>264</v>
       </c>
@@ -61959,7 +61958,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="129" spans="1:21" hidden="1">
+    <row r="129" spans="1:21">
       <c r="A129" s="15" t="s">
         <v>264</v>
       </c>
@@ -62018,7 +62017,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="130" spans="1:21" hidden="1">
+    <row r="130" spans="1:21">
       <c r="A130" s="15" t="s">
         <v>264</v>
       </c>
@@ -62077,7 +62076,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="131" spans="1:21" hidden="1">
+    <row r="131" spans="1:21">
       <c r="A131" s="15" t="s">
         <v>264</v>
       </c>
@@ -62136,7 +62135,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="132" spans="1:21" hidden="1">
+    <row r="132" spans="1:21">
       <c r="A132" s="15" t="s">
         <v>264</v>
       </c>
@@ -62195,7 +62194,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="133" spans="1:21" hidden="1">
+    <row r="133" spans="1:21">
       <c r="A133" s="15" t="s">
         <v>264</v>
       </c>
@@ -62254,7 +62253,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="134" spans="1:21" hidden="1">
+    <row r="134" spans="1:21">
       <c r="A134" s="15" t="s">
         <v>264</v>
       </c>
@@ -62313,7 +62312,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="135" spans="1:21" hidden="1">
+    <row r="135" spans="1:21">
       <c r="A135" s="15" t="s">
         <v>238</v>
       </c>
@@ -62372,7 +62371,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="136" spans="1:21" hidden="1">
+    <row r="136" spans="1:21">
       <c r="A136" s="15" t="s">
         <v>238</v>
       </c>
@@ -62431,7 +62430,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="137" spans="1:21" hidden="1">
+    <row r="137" spans="1:21">
       <c r="A137" s="15" t="s">
         <v>238</v>
       </c>
@@ -62490,7 +62489,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="138" spans="1:21" hidden="1">
+    <row r="138" spans="1:21">
       <c r="A138" s="15" t="s">
         <v>238</v>
       </c>
@@ -62549,7 +62548,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="139" spans="1:21" hidden="1">
+    <row r="139" spans="1:21">
       <c r="A139" s="15" t="s">
         <v>238</v>
       </c>
@@ -62608,7 +62607,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="140" spans="1:21" hidden="1">
+    <row r="140" spans="1:21">
       <c r="A140" s="15" t="s">
         <v>238</v>
       </c>
@@ -62667,7 +62666,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="141" spans="1:21" hidden="1">
+    <row r="141" spans="1:21">
       <c r="A141" s="15" t="s">
         <v>238</v>
       </c>
@@ -62726,7 +62725,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="142" spans="1:21" hidden="1">
+    <row r="142" spans="1:21">
       <c r="A142" s="15" t="s">
         <v>238</v>
       </c>
@@ -62785,7 +62784,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="143" spans="1:21" hidden="1">
+    <row r="143" spans="1:21">
       <c r="A143" s="15" t="s">
         <v>238</v>
       </c>
@@ -62844,7 +62843,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="144" spans="1:21" hidden="1">
+    <row r="144" spans="1:21">
       <c r="A144" s="15" t="s">
         <v>238</v>
       </c>
@@ -62903,7 +62902,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="145" spans="1:21" hidden="1">
+    <row r="145" spans="1:21">
       <c r="A145" s="15" t="s">
         <v>238</v>
       </c>
@@ -62962,7 +62961,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="146" spans="1:21" hidden="1">
+    <row r="146" spans="1:21">
       <c r="A146" s="15" t="s">
         <v>238</v>
       </c>
@@ -63021,7 +63020,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="147" spans="1:21" hidden="1">
+    <row r="147" spans="1:21">
       <c r="A147" s="15" t="s">
         <v>238</v>
       </c>
@@ -63080,7 +63079,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="148" spans="1:21" hidden="1">
+    <row r="148" spans="1:21">
       <c r="A148" s="15" t="s">
         <v>238</v>
       </c>
@@ -63139,7 +63138,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="149" spans="1:21" hidden="1">
+    <row r="149" spans="1:21">
       <c r="A149" s="15" t="s">
         <v>238</v>
       </c>
@@ -63198,7 +63197,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="150" spans="1:21" hidden="1">
+    <row r="150" spans="1:21">
       <c r="A150" s="15" t="s">
         <v>238</v>
       </c>
@@ -63257,7 +63256,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="151" spans="1:21" hidden="1">
+    <row r="151" spans="1:21">
       <c r="A151" s="15" t="s">
         <v>238</v>
       </c>
@@ -63316,7 +63315,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="152" spans="1:21" hidden="1">
+    <row r="152" spans="1:21">
       <c r="A152" s="15" t="s">
         <v>238</v>
       </c>
@@ -63375,7 +63374,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="153" spans="1:21" hidden="1">
+    <row r="153" spans="1:21">
       <c r="A153" s="15" t="s">
         <v>238</v>
       </c>
@@ -63434,7 +63433,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="154" spans="1:21" hidden="1">
+    <row r="154" spans="1:21">
       <c r="A154" s="15" t="s">
         <v>238</v>
       </c>
@@ -63493,7 +63492,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="155" spans="1:21" hidden="1">
+    <row r="155" spans="1:21">
       <c r="A155" s="15" t="s">
         <v>238</v>
       </c>
@@ -63552,7 +63551,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="156" spans="1:21" hidden="1">
+    <row r="156" spans="1:21">
       <c r="A156" s="15" t="s">
         <v>238</v>
       </c>
@@ -63611,7 +63610,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="157" spans="1:21" hidden="1">
+    <row r="157" spans="1:21">
       <c r="A157" s="15" t="s">
         <v>238</v>
       </c>
@@ -63670,7 +63669,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="158" spans="1:21" hidden="1">
+    <row r="158" spans="1:21">
       <c r="A158" s="15" t="s">
         <v>238</v>
       </c>
@@ -63729,7 +63728,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="159" spans="1:21" hidden="1">
+    <row r="159" spans="1:21">
       <c r="A159" s="15" t="s">
         <v>238</v>
       </c>
@@ -63788,7 +63787,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="160" spans="1:21" hidden="1">
+    <row r="160" spans="1:21">
       <c r="A160" s="15" t="s">
         <v>238</v>
       </c>
@@ -63847,7 +63846,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="161" spans="1:21" hidden="1">
+    <row r="161" spans="1:21">
       <c r="A161" s="15" t="s">
         <v>238</v>
       </c>
@@ -63906,7 +63905,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="162" spans="1:21" hidden="1">
+    <row r="162" spans="1:21">
       <c r="A162" s="15" t="s">
         <v>238</v>
       </c>
@@ -63965,7 +63964,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="163" spans="1:21" hidden="1">
+    <row r="163" spans="1:21">
       <c r="A163" s="15" t="s">
         <v>238</v>
       </c>
@@ -64024,7 +64023,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="164" spans="1:21" hidden="1">
+    <row r="164" spans="1:21">
       <c r="A164" s="15" t="s">
         <v>238</v>
       </c>
@@ -64083,7 +64082,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="165" spans="1:21" hidden="1">
+    <row r="165" spans="1:21">
       <c r="A165" s="15" t="s">
         <v>238</v>
       </c>
@@ -64142,7 +64141,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="166" spans="1:21" hidden="1">
+    <row r="166" spans="1:21">
       <c r="A166" s="15" t="s">
         <v>238</v>
       </c>
@@ -64201,7 +64200,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="167" spans="1:21" hidden="1">
+    <row r="167" spans="1:21">
       <c r="A167" s="15" t="s">
         <v>238</v>
       </c>
@@ -64260,7 +64259,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="168" spans="1:21" hidden="1">
+    <row r="168" spans="1:21">
       <c r="A168" s="15" t="s">
         <v>238</v>
       </c>
@@ -64319,7 +64318,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="169" spans="1:21" hidden="1">
+    <row r="169" spans="1:21">
       <c r="A169" s="15" t="s">
         <v>238</v>
       </c>
@@ -64378,7 +64377,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="170" spans="1:21" hidden="1">
+    <row r="170" spans="1:21">
       <c r="A170" s="15" t="s">
         <v>238</v>
       </c>
@@ -64437,7 +64436,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="171" spans="1:21" hidden="1">
+    <row r="171" spans="1:21">
       <c r="A171" s="15" t="s">
         <v>238</v>
       </c>
@@ -64496,7 +64495,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="172" spans="1:21" hidden="1">
+    <row r="172" spans="1:21">
       <c r="A172" s="15" t="s">
         <v>238</v>
       </c>
@@ -64555,7 +64554,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="173" spans="1:21" hidden="1">
+    <row r="173" spans="1:21">
       <c r="A173" s="15" t="s">
         <v>238</v>
       </c>
@@ -64614,7 +64613,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="174" spans="1:21" hidden="1">
+    <row r="174" spans="1:21">
       <c r="A174" s="15" t="s">
         <v>238</v>
       </c>
@@ -64673,7 +64672,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="175" spans="1:21" hidden="1">
+    <row r="175" spans="1:21">
       <c r="A175" s="15" t="s">
         <v>238</v>
       </c>
@@ -64732,7 +64731,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="176" spans="1:21" hidden="1">
+    <row r="176" spans="1:21">
       <c r="A176" s="15" t="s">
         <v>238</v>
       </c>
@@ -64791,7 +64790,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="177" spans="1:21" hidden="1">
+    <row r="177" spans="1:21">
       <c r="A177" s="15" t="s">
         <v>238</v>
       </c>
@@ -64850,7 +64849,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="178" spans="1:21" hidden="1">
+    <row r="178" spans="1:21">
       <c r="A178" s="15" t="s">
         <v>238</v>
       </c>
@@ -64909,7 +64908,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="179" spans="1:21" hidden="1">
+    <row r="179" spans="1:21">
       <c r="A179" s="15" t="s">
         <v>238</v>
       </c>
@@ -64968,7 +64967,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="180" spans="1:21" hidden="1">
+    <row r="180" spans="1:21">
       <c r="A180" s="15" t="s">
         <v>238</v>
       </c>
@@ -65027,7 +65026,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="181" spans="1:21" hidden="1">
+    <row r="181" spans="1:21">
       <c r="A181" s="15" t="s">
         <v>238</v>
       </c>
@@ -65086,7 +65085,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="182" spans="1:21" hidden="1">
+    <row r="182" spans="1:21">
       <c r="A182" s="15" t="s">
         <v>238</v>
       </c>
@@ -65145,7 +65144,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="183" spans="1:21" hidden="1">
+    <row r="183" spans="1:21">
       <c r="A183" s="15" t="s">
         <v>238</v>
       </c>
@@ -65204,7 +65203,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="184" spans="1:21" hidden="1">
+    <row r="184" spans="1:21">
       <c r="A184" s="15" t="s">
         <v>238</v>
       </c>
@@ -65263,7 +65262,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="185" spans="1:21" hidden="1">
+    <row r="185" spans="1:21">
       <c r="A185" s="15" t="s">
         <v>238</v>
       </c>
@@ -65322,7 +65321,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="186" spans="1:21" hidden="1">
+    <row r="186" spans="1:21">
       <c r="A186" s="15" t="s">
         <v>238</v>
       </c>
@@ -65381,7 +65380,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="187" spans="1:21" hidden="1">
+    <row r="187" spans="1:21">
       <c r="A187" s="15" t="s">
         <v>161</v>
       </c>
@@ -65440,7 +65439,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="188" spans="1:21" hidden="1">
+    <row r="188" spans="1:21">
       <c r="A188" s="15" t="s">
         <v>161</v>
       </c>
@@ -65499,7 +65498,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="189" spans="1:21" hidden="1">
+    <row r="189" spans="1:21">
       <c r="A189" s="15" t="s">
         <v>203</v>
       </c>
@@ -65558,7 +65557,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="190" spans="1:21" hidden="1">
+    <row r="190" spans="1:21">
       <c r="A190" s="15" t="s">
         <v>203</v>
       </c>
@@ -65617,7 +65616,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="191" spans="1:21" hidden="1">
+    <row r="191" spans="1:21">
       <c r="A191" s="15" t="s">
         <v>203</v>
       </c>
@@ -65676,7 +65675,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="192" spans="1:21" hidden="1">
+    <row r="192" spans="1:21">
       <c r="A192" s="15" t="s">
         <v>203</v>
       </c>
@@ -65735,7 +65734,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="193" spans="1:21" hidden="1">
+    <row r="193" spans="1:21">
       <c r="A193" s="15" t="s">
         <v>203</v>
       </c>
@@ -65794,7 +65793,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="194" spans="1:21" hidden="1">
+    <row r="194" spans="1:21">
       <c r="A194" s="15" t="s">
         <v>203</v>
       </c>
@@ -65853,7 +65852,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="195" spans="1:21" hidden="1">
+    <row r="195" spans="1:21">
       <c r="A195" s="15" t="s">
         <v>203</v>
       </c>
@@ -65912,7 +65911,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="196" spans="1:21" hidden="1">
+    <row r="196" spans="1:21">
       <c r="A196" s="15" t="s">
         <v>203</v>
       </c>
@@ -65973,7 +65972,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="197" spans="1:21" hidden="1">
+    <row r="197" spans="1:21">
       <c r="A197" s="15" t="s">
         <v>203</v>
       </c>
@@ -66034,7 +66033,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="198" spans="1:21" hidden="1">
+    <row r="198" spans="1:21">
       <c r="A198" s="15" t="s">
         <v>727</v>
       </c>
@@ -66093,7 +66092,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="199" spans="1:21" hidden="1">
+    <row r="199" spans="1:21">
       <c r="A199" s="15" t="s">
         <v>727</v>
       </c>
@@ -66152,7 +66151,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="200" spans="1:21" hidden="1">
+    <row r="200" spans="1:21">
       <c r="A200" s="15" t="s">
         <v>727</v>
       </c>
@@ -66211,7 +66210,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="201" spans="1:21" hidden="1">
+    <row r="201" spans="1:21">
       <c r="A201" s="15" t="s">
         <v>727</v>
       </c>
@@ -66270,7 +66269,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="202" spans="1:21" hidden="1">
+    <row r="202" spans="1:21">
       <c r="A202" s="15" t="s">
         <v>727</v>
       </c>
@@ -66329,7 +66328,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="203" spans="1:21" hidden="1">
+    <row r="203" spans="1:21">
       <c r="A203" s="15" t="s">
         <v>727</v>
       </c>
@@ -66388,7 +66387,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="204" spans="1:21" hidden="1">
+    <row r="204" spans="1:21">
       <c r="A204" s="15" t="s">
         <v>727</v>
       </c>
@@ -66447,7 +66446,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="205" spans="1:21" hidden="1">
+    <row r="205" spans="1:21">
       <c r="A205" s="15" t="s">
         <v>727</v>
       </c>
@@ -66506,7 +66505,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="206" spans="1:21" hidden="1">
+    <row r="206" spans="1:21">
       <c r="A206" s="15" t="s">
         <v>727</v>
       </c>
@@ -66565,7 +66564,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="207" spans="1:21" hidden="1">
+    <row r="207" spans="1:21">
       <c r="A207" s="15" t="s">
         <v>727</v>
       </c>
@@ -66624,7 +66623,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="208" spans="1:21" hidden="1">
+    <row r="208" spans="1:21">
       <c r="A208" s="15" t="s">
         <v>705</v>
       </c>
@@ -66685,7 +66684,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="209" spans="1:21" hidden="1">
+    <row r="209" spans="1:21">
       <c r="A209" s="15" t="s">
         <v>705</v>
       </c>
@@ -66746,7 +66745,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="210" spans="1:21" hidden="1">
+    <row r="210" spans="1:21">
       <c r="A210" s="15" t="s">
         <v>705</v>
       </c>
@@ -66807,7 +66806,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="211" spans="1:21" hidden="1">
+    <row r="211" spans="1:21">
       <c r="A211" s="15" t="s">
         <v>728</v>
       </c>
@@ -66836,10 +66835,10 @@
         <v>108</v>
       </c>
       <c r="J211" s="15" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="K211" s="15" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="L211" s="15" t="s">
         <v>156</v>
@@ -66848,25 +66847,25 @@
         <v>12</v>
       </c>
       <c r="N211" s="15">
-        <v>1.1000000000000001</v>
+        <v>0.35</v>
       </c>
       <c r="O211" s="15">
-        <v>0.4</v>
+        <v>0.08</v>
       </c>
       <c r="Q211" s="15">
         <v>12</v>
       </c>
       <c r="R211" s="15">
-        <v>1.1000000000000001</v>
+        <v>0.61</v>
       </c>
       <c r="S211" s="15">
         <v>0.4</v>
       </c>
       <c r="U211" s="14" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="212" spans="1:21" hidden="1">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="212" spans="1:21">
       <c r="A212" s="15" t="s">
         <v>728</v>
       </c>
@@ -66895,10 +66894,10 @@
         <v>108</v>
       </c>
       <c r="J212" s="15" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="K212" s="15" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="L212" s="15" t="s">
         <v>156</v>
@@ -66907,25 +66906,25 @@
         <v>12</v>
       </c>
       <c r="N212" s="15">
-        <v>0.35</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="O212" s="15">
-        <v>0.08</v>
+        <v>0.4</v>
       </c>
       <c r="Q212" s="15">
         <v>12</v>
       </c>
       <c r="R212" s="15">
-        <v>0.61</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="S212" s="15">
         <v>0.4</v>
       </c>
       <c r="U212" s="14" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="213" spans="1:21" hidden="1">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="213" spans="1:21">
       <c r="A213" s="15" t="s">
         <v>728</v>
       </c>
@@ -66984,7 +66983,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="214" spans="1:21" hidden="1">
+    <row r="214" spans="1:21">
       <c r="A214" s="15" t="s">
         <v>728</v>
       </c>
@@ -67043,7 +67042,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="215" spans="1:21" hidden="1">
+    <row r="215" spans="1:21">
       <c r="A215" s="15" t="s">
         <v>729</v>
       </c>
@@ -67102,7 +67101,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="216" spans="1:21" hidden="1">
+    <row r="216" spans="1:21">
       <c r="A216" s="15" t="s">
         <v>729</v>
       </c>
@@ -67161,7 +67160,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="217" spans="1:21" hidden="1">
+    <row r="217" spans="1:21">
       <c r="A217" s="15" t="s">
         <v>729</v>
       </c>
@@ -67220,7 +67219,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="218" spans="1:21" hidden="1">
+    <row r="218" spans="1:21">
       <c r="A218" s="15" t="s">
         <v>729</v>
       </c>
@@ -67279,7 +67278,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="219" spans="1:21" hidden="1">
+    <row r="219" spans="1:21">
       <c r="A219" s="15" t="s">
         <v>729</v>
       </c>
@@ -67338,7 +67337,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="220" spans="1:21" hidden="1">
+    <row r="220" spans="1:21">
       <c r="A220" s="15" t="s">
         <v>729</v>
       </c>
@@ -67397,7 +67396,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="221" spans="1:21" hidden="1">
+    <row r="221" spans="1:21">
       <c r="A221" s="15" t="s">
         <v>729</v>
       </c>
@@ -67456,7 +67455,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="222" spans="1:21" hidden="1">
+    <row r="222" spans="1:21">
       <c r="A222" s="15" t="s">
         <v>729</v>
       </c>
@@ -67515,7 +67514,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="223" spans="1:21" hidden="1">
+    <row r="223" spans="1:21">
       <c r="A223" s="15" t="s">
         <v>729</v>
       </c>
@@ -67574,7 +67573,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="224" spans="1:21" hidden="1">
+    <row r="224" spans="1:21">
       <c r="A224" s="15" t="s">
         <v>729</v>
       </c>
@@ -67633,7 +67632,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="225" spans="1:21" hidden="1">
+    <row r="225" spans="1:21">
       <c r="A225" s="15" t="s">
         <v>730</v>
       </c>
@@ -67692,7 +67691,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="226" spans="1:21" hidden="1">
+    <row r="226" spans="1:21">
       <c r="A226" s="15" t="s">
         <v>730</v>
       </c>
@@ -67751,7 +67750,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="227" spans="1:21" hidden="1">
+    <row r="227" spans="1:21">
       <c r="A227" s="15" t="s">
         <v>731</v>
       </c>
@@ -67810,7 +67809,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="228" spans="1:21" hidden="1">
+    <row r="228" spans="1:21">
       <c r="A228" s="15" t="s">
         <v>731</v>
       </c>
@@ -67869,7 +67868,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="229" spans="1:21" hidden="1">
+    <row r="229" spans="1:21">
       <c r="A229" s="15" t="s">
         <v>732</v>
       </c>
@@ -67931,7 +67930,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="230" spans="1:21" hidden="1">
+    <row r="230" spans="1:21">
       <c r="A230" s="15" t="s">
         <v>732</v>
       </c>
@@ -67993,7 +67992,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="231" spans="1:21" hidden="1">
+    <row r="231" spans="1:21">
       <c r="A231" s="15" t="s">
         <v>732</v>
       </c>
@@ -68055,7 +68054,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="232" spans="1:21" hidden="1">
+    <row r="232" spans="1:21">
       <c r="A232" s="15" t="s">
         <v>732</v>
       </c>
@@ -68117,7 +68116,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="233" spans="1:21" hidden="1">
+    <row r="233" spans="1:21">
       <c r="A233" s="15" t="s">
         <v>732</v>
       </c>
@@ -68179,7 +68178,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="234" spans="1:21" hidden="1">
+    <row r="234" spans="1:21">
       <c r="A234" s="15" t="s">
         <v>732</v>
       </c>
@@ -68241,7 +68240,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="235" spans="1:21" hidden="1">
+    <row r="235" spans="1:21">
       <c r="A235" s="15" t="s">
         <v>732</v>
       </c>
@@ -68303,7 +68302,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="236" spans="1:21" hidden="1">
+    <row r="236" spans="1:21">
       <c r="A236" s="15" t="s">
         <v>732</v>
       </c>
@@ -68365,24 +68364,13 @@
         <v>430</v>
       </c>
     </row>
-    <row r="237" spans="1:21" hidden="1">
+    <row r="237" spans="1:21">
       <c r="D237" s="13"/>
     </row>
-    <row r="238" spans="1:21" hidden="1">
+    <row r="238" spans="1:21">
       <c r="D238" s="13"/>
     </row>
-    <row r="239" spans="1:21" hidden="1"/>
   </sheetData>
-  <autoFilter ref="A1:U239" xr:uid="{00000000-0001-0000-0100-000000000000}">
-    <filterColumn colId="2">
-      <filters>
-        <filter val="study543"/>
-      </filters>
-    </filterColumn>
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:U238">
-      <sortCondition ref="A1:A239"/>
-    </sortState>
-  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
